--- a/Plots/Comparison Table of k and p Values (root at local minimum).xlsx
+++ b/Plots/Comparison Table of k and p Values (root at local minimum).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/mepstein_olin_edu/Documents/Desktop/Applied Math/Assignment-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/mepstein_olin_edu/Documents/Desktop/Applied Math/Assignment-1/Plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7112020F-FEC7-459C-AB62-006F9C349AF2}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8F9AFA6-DDA0-48DA-A263-E55DB710D533}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,18 +44,6 @@
     <t>Method</t>
   </si>
   <si>
-    <t>Predicted k value</t>
-  </si>
-  <si>
-    <t>Measured k value</t>
-  </si>
-  <si>
-    <t>Predicted p value</t>
-  </si>
-  <si>
-    <t>Measured p value</t>
-  </si>
-  <si>
     <t>Newton's Method</t>
   </si>
   <si>
@@ -69,6 +57,18 @@
   </si>
   <si>
     <t>Inf</t>
+  </si>
+  <si>
+    <t>Predicted k value (-)</t>
+  </si>
+  <si>
+    <t>Measured k value (-)</t>
+  </si>
+  <si>
+    <t>Predicted p value (-)</t>
+  </si>
+  <si>
+    <t>Measured p value (-)</t>
   </si>
 </sst>
 </file>
@@ -520,15 +520,15 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -540,27 +540,27 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="2">
-        <v>6.9000000000000006E-2</v>
+        <v>0.62429999999999997</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
@@ -571,13 +571,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>0.76639999999999997</v>
+        <v>0.76629999999999998</v>
       </c>
       <c r="D4" s="3">
         <v>1.6</v>
